--- a/files/01_KIBB_SegmentPnL.xlsx
+++ b/files/01_KIBB_SegmentPnL.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenanga Investment Bank Berhad - Group Monthly Operating Cost (RM '000)</t>
+          <t>Contoso Investment Bank Berhad - Group Monthly Operating Cost (RM '000)</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>CEO, Kenanga Investors</t>
+          <t>CEO, Contoso Investors</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1640,7 +1640,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIBB Segment Revenue (RM '000) - FY2026 YTD</t>
+          <t>Contoso Segment Revenue (RM '000) - FY2026 YTD</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIBB Group KPIs - FY2026 YTD</t>
+          <t>Contoso Group KPIs - FY2026 YTD</t>
         </is>
       </c>
     </row>

--- a/files/01_KIBB_SegmentPnL.xlsx
+++ b/files/01_KIBB_SegmentPnL.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FY2026 - Source: Group Finance - Confidential: Board Risk Committee</t>
+          <t>FY2025 (Final Audited) - Source: Group Finance - Confidential: Board Risk Committee</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Contoso Segment Revenue (RM '000) - FY2026 YTD</t>
+          <t>Contoso Segment Revenue (RM '000) - FY2025 Full Year</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Contoso Group KPIs - FY2026 YTD</t>
+          <t>Contoso Group KPIs - FY2025 Full Year</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>FY2026 YTD</t>
+          <t>FY2025 Actual</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>FY2026 Budget / Threshold</t>
+          <t>FY2025 Budget / Threshold</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Slipped from 25.3% (FY24) - Rakuten platform stability</t>
+          <t>Slipped from 25.3% (FY24) - retail trading platform stability issues</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>KDi GO uptake slower than plan</t>
+          <t>Digital wealth platform uptake slower than plan</t>
         </is>
       </c>
     </row>
